--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Léo\Documents\Pathfinder\Campagne des Tempêtes\Construction de royaumes\Simulations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB43F0D2-4F52-404E-8EDA-A8C9A05E6982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A625B4-7149-4767-BC4B-686C8FD05A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33885" yWindow="2025" windowWidth="28125" windowHeight="14760" xr2:uid="{CBB80B22-E302-4148-88F2-18F13870AE8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CBB80B22-E302-4148-88F2-18F13870AE8F}"/>
   </bookViews>
   <sheets>
     <sheet name="projets" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="250">
   <si>
     <t>id</t>
   </si>
@@ -155,9 +155,6 @@
     <t>BATIMENT CAMP DE FIBRE</t>
   </si>
   <si>
-    <t>PIERRE=4</t>
-  </si>
-  <si>
     <t>workshop_construction</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>BATIMENT ATELIER</t>
   </si>
   <si>
-    <t>FIBRE=4</t>
-  </si>
-  <si>
     <t>workshop_production_plank</t>
   </si>
   <si>
@@ -333,6 +327,468 @@
   </si>
   <si>
     <t>grants</t>
+  </si>
+  <si>
+    <t>bakery_construction</t>
+  </si>
+  <si>
+    <t>Boulangerie</t>
+  </si>
+  <si>
+    <t>PLANCHE=2;BRIQUE=4</t>
+  </si>
+  <si>
+    <t>BATIMENT BOULANGERIE</t>
+  </si>
+  <si>
+    <t>bakery_production</t>
+  </si>
+  <si>
+    <t>Brasserie</t>
+  </si>
+  <si>
+    <t>brewery_construction</t>
+  </si>
+  <si>
+    <t>brewery_production</t>
+  </si>
+  <si>
+    <t>BATIMENT BRASSERIE</t>
+  </si>
+  <si>
+    <t>CEREALE=6</t>
+  </si>
+  <si>
+    <t>BIERE=12</t>
+  </si>
+  <si>
+    <t>PAIN=16;NOURRITURE=16</t>
+  </si>
+  <si>
+    <t>tailor_construction</t>
+  </si>
+  <si>
+    <t>tailor_production</t>
+  </si>
+  <si>
+    <t>Tailleur</t>
+  </si>
+  <si>
+    <t>ranch_construction</t>
+  </si>
+  <si>
+    <t>ranch_production</t>
+  </si>
+  <si>
+    <t>Ranch</t>
+  </si>
+  <si>
+    <t>smelter_construction</t>
+  </si>
+  <si>
+    <t>smelter_production</t>
+  </si>
+  <si>
+    <t>trading_post_construction</t>
+  </si>
+  <si>
+    <t>armory_construction</t>
+  </si>
+  <si>
+    <t>armory_production_weapon</t>
+  </si>
+  <si>
+    <t>armory_production_armour</t>
+  </si>
+  <si>
+    <t>tavern_construction</t>
+  </si>
+  <si>
+    <t>temple_construction</t>
+  </si>
+  <si>
+    <t>storage_construction</t>
+  </si>
+  <si>
+    <t>dam_construction</t>
+  </si>
+  <si>
+    <t>house_construction</t>
+  </si>
+  <si>
+    <t>comfortable_house_construction</t>
+  </si>
+  <si>
+    <t>rain_engine_construction</t>
+  </si>
+  <si>
+    <t>runemaker_upgrade_armor</t>
+  </si>
+  <si>
+    <t>runemaker_upgrade_jewelry</t>
+  </si>
+  <si>
+    <t>runemaker_upgrade_weapon</t>
+  </si>
+  <si>
+    <t>runemaker_construction</t>
+  </si>
+  <si>
+    <t>herbalist_construction</t>
+  </si>
+  <si>
+    <t>herbalist_production</t>
+  </si>
+  <si>
+    <t>potion_brewer_construction</t>
+  </si>
+  <si>
+    <t>arena_construction</t>
+  </si>
+  <si>
+    <t>library_construction</t>
+  </si>
+  <si>
+    <t>bathouse_construction</t>
+  </si>
+  <si>
+    <t>corrupted_altar_construction</t>
+  </si>
+  <si>
+    <t>observation_tower_construction</t>
+  </si>
+  <si>
+    <t>toolmaker_construction</t>
+  </si>
+  <si>
+    <t>toolmaker_production</t>
+  </si>
+  <si>
+    <t>Cuisine</t>
+  </si>
+  <si>
+    <t>Tour de mage</t>
+  </si>
+  <si>
+    <t>Herboriste</t>
+  </si>
+  <si>
+    <t>Brasseur de potions</t>
+  </si>
+  <si>
+    <t>Arène</t>
+  </si>
+  <si>
+    <t>Maître des runes</t>
+  </si>
+  <si>
+    <t>Moteur de pluie</t>
+  </si>
+  <si>
+    <t>Fonderie</t>
+  </si>
+  <si>
+    <t>Comptoir commercial</t>
+  </si>
+  <si>
+    <t>Armurerie</t>
+  </si>
+  <si>
+    <t>Taverne</t>
+  </si>
+  <si>
+    <t>Temple</t>
+  </si>
+  <si>
+    <t>Entrepôt</t>
+  </si>
+  <si>
+    <t>Barrage</t>
+  </si>
+  <si>
+    <t>Habitation</t>
+  </si>
+  <si>
+    <t>Bibliothèque</t>
+  </si>
+  <si>
+    <t>Bains publics</t>
+  </si>
+  <si>
+    <t>Autel corrompu</t>
+  </si>
+  <si>
+    <t>Tour d'observation</t>
+  </si>
+  <si>
+    <t>Quincaillerie</t>
+  </si>
+  <si>
+    <t>palissade_construction</t>
+  </si>
+  <si>
+    <t>wall_construction</t>
+  </si>
+  <si>
+    <t>kitchen_construction</t>
+  </si>
+  <si>
+    <t>mage_tower_construction</t>
+  </si>
+  <si>
+    <t>advanced_workshop_construction</t>
+  </si>
+  <si>
+    <t>traps_construction</t>
+  </si>
+  <si>
+    <t>mote_construction</t>
+  </si>
+  <si>
+    <t>Défenses</t>
+  </si>
+  <si>
+    <t>Atelier avancé</t>
+  </si>
+  <si>
+    <t>city_hall_construction</t>
+  </si>
+  <si>
+    <t>Hotel de ville</t>
+  </si>
+  <si>
+    <t>Produire armure</t>
+  </si>
+  <si>
+    <t>Produire arme</t>
+  </si>
+  <si>
+    <t>potion_brewer_production_medicine</t>
+  </si>
+  <si>
+    <t>potion_brewer_production_potion</t>
+  </si>
+  <si>
+    <t>Produire médicament</t>
+  </si>
+  <si>
+    <t>Produire potions</t>
+  </si>
+  <si>
+    <t>FIBRE=6</t>
+  </si>
+  <si>
+    <t>PIERRE=6</t>
+  </si>
+  <si>
+    <t>Améliorer</t>
+  </si>
+  <si>
+    <t>BATIMENT TAILLEUR</t>
+  </si>
+  <si>
+    <t>BATIMENT RANCH</t>
+  </si>
+  <si>
+    <t>BATIMENT FONDERIE</t>
+  </si>
+  <si>
+    <t>BATIMENT COMPTOIR COMMERCIAL</t>
+  </si>
+  <si>
+    <t>BATIMENT ARMURERIE</t>
+  </si>
+  <si>
+    <t>BATIMENT TAVERNE</t>
+  </si>
+  <si>
+    <t>BATIMENT TEMPLE</t>
+  </si>
+  <si>
+    <t>BATIMENT BARRAGE</t>
+  </si>
+  <si>
+    <t>BATIMENT MOTEUR DE PLUIE</t>
+  </si>
+  <si>
+    <t>BATIMENT HERBORISTE</t>
+  </si>
+  <si>
+    <t>VETEMENTS=4</t>
+  </si>
+  <si>
+    <t>BOIS=4;FIBRE=4</t>
+  </si>
+  <si>
+    <t>NOURRITURE=2</t>
+  </si>
+  <si>
+    <t>MINERAI=6</t>
+  </si>
+  <si>
+    <t>PLANCHE=3;TEXTILE=4</t>
+  </si>
+  <si>
+    <t>ARMURE=2</t>
+  </si>
+  <si>
+    <t>METAL=2;BRIQUE=2;PLANCHE=3</t>
+  </si>
+  <si>
+    <t>PLANCHE=4;BRIQUE=2</t>
+  </si>
+  <si>
+    <t>PLANCHE=4;BRIQUE=4</t>
+  </si>
+  <si>
+    <t>BRIQUE=4</t>
+  </si>
+  <si>
+    <t>ARME=2</t>
+  </si>
+  <si>
+    <t>BATIMENT BRASSEUR DE POTIONS</t>
+  </si>
+  <si>
+    <t>BATIMENT BAINS PUBLICS</t>
+  </si>
+  <si>
+    <t>BATIMENT AUTEL CORROMPU</t>
+  </si>
+  <si>
+    <t>BATIMENT ENTREPOT</t>
+  </si>
+  <si>
+    <t>BRIQUE=6</t>
+  </si>
+  <si>
+    <t>PLANCHE=5</t>
+  </si>
+  <si>
+    <t>PLANCHE=8;BRIQUE=12</t>
+  </si>
+  <si>
+    <t>PLANCHE=4;TEXTILE=2</t>
+  </si>
+  <si>
+    <t>PLANCHE=2;BRIQUE=4;TEXTILE=4</t>
+  </si>
+  <si>
+    <t>BATIMENT MAISON</t>
+  </si>
+  <si>
+    <t>BATIMENT MAISON CONFORTABLE</t>
+  </si>
+  <si>
+    <t>BATIMENT MAITRE DES RUNES</t>
+  </si>
+  <si>
+    <t>RESSOURCE</t>
+  </si>
+  <si>
+    <t>PIERRE=1;ARME=1</t>
+  </si>
+  <si>
+    <t>PIERRE=1;BIJOU=1</t>
+  </si>
+  <si>
+    <t>PIERRE=1;ARMURE=1</t>
+  </si>
+  <si>
+    <t>BOIS=4;TEXTILE=2</t>
+  </si>
+  <si>
+    <t>INGREDIENT=2</t>
+  </si>
+  <si>
+    <t>ARMURE ENCHANTEE=1</t>
+  </si>
+  <si>
+    <t>ARME ENCHANTEE=1</t>
+  </si>
+  <si>
+    <t>BIJOU ENCHANTE=1</t>
+  </si>
+  <si>
+    <t>BRIQUE=6;TEXTILE=4;METAL=1</t>
+  </si>
+  <si>
+    <t>POTION=2</t>
+  </si>
+  <si>
+    <t>INGREDIENT=2;BOIS=2</t>
+  </si>
+  <si>
+    <t>MEDICAMENT=2</t>
+  </si>
+  <si>
+    <t>BATIMENT ARENE</t>
+  </si>
+  <si>
+    <t>BATIMENT BILIOTHEQUE</t>
+  </si>
+  <si>
+    <t>BATIMENT TOUR OBSERVATIOn</t>
+  </si>
+  <si>
+    <t>BATIMENT QUINCAILLERIE</t>
+  </si>
+  <si>
+    <t>BATIMENT PALISSADE</t>
+  </si>
+  <si>
+    <t>BATIMENT FOSSE</t>
+  </si>
+  <si>
+    <t>BATIMENT MURAILLE</t>
+  </si>
+  <si>
+    <t>BATIMENT CUISINE</t>
+  </si>
+  <si>
+    <t>BATIMENT TOUR DE MAGE</t>
+  </si>
+  <si>
+    <t>BATIMENT HOTEL DE VILLE</t>
+  </si>
+  <si>
+    <t>BATIMENT ATELIER AVANCE</t>
+  </si>
+  <si>
+    <t>OUTIL=2</t>
+  </si>
+  <si>
+    <t>INGREDIENT=2;CHARBON=1;OUTIL=1</t>
+  </si>
+  <si>
+    <t>METAL=2;CHARBON=2;OUTIL=2</t>
+  </si>
+  <si>
+    <t>METAL=2;BOIS=2;CHARBON=2;OUTIL=2</t>
+  </si>
+  <si>
+    <t>METAL=2;BOIS=2</t>
+  </si>
+  <si>
+    <t>PLANCHE=6;BRIQUE=6;TEXTILE=6</t>
+  </si>
+  <si>
+    <t>BOIS=16</t>
+  </si>
+  <si>
+    <t>BRIQUE=24</t>
+  </si>
+  <si>
+    <t>OUTIL=4</t>
+  </si>
+  <si>
+    <t>PIEGE=2</t>
+  </si>
+  <si>
+    <t>FIBRE=2;BOIS=1;PIERRE=1</t>
+  </si>
+  <si>
+    <t>BOIS=6</t>
   </si>
 </sst>
 </file>
@@ -368,7 +824,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -704,14 +1161,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B33A7991-BA04-471F-B7E5-9B4EA1B69C5B}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.140625" customWidth="1"/>
     <col min="5" max="5" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="33.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.140625" customWidth="1"/>
   </cols>
@@ -739,7 +1197,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -819,7 +1277,7 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -862,7 +1320,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -871,7 +1329,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>249</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
@@ -905,7 +1363,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -914,7 +1372,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="I9" t="s">
         <v>9</v>
@@ -948,7 +1406,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -957,7 +1415,7 @@
         <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>178</v>
       </c>
       <c r="I11" t="s">
         <v>9</v>
@@ -965,22 +1423,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="H12" t="s">
         <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" t="s">
-        <v>42</v>
       </c>
       <c r="I12" t="s">
         <v>13</v>
@@ -988,25 +1446,25 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I13" t="s">
         <v>9</v>
@@ -1014,25 +1472,25 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I14" t="s">
         <v>9</v>
@@ -1040,25 +1498,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
         <v>41</v>
       </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I15" t="s">
         <v>9</v>
@@ -1066,10 +1524,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -1078,10 +1536,10 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
         <v>58</v>
-      </c>
-      <c r="H16" t="s">
-        <v>60</v>
       </c>
       <c r="I16" t="s">
         <v>13</v>
@@ -1089,25 +1547,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="I17" t="s">
         <v>9</v>
@@ -1115,10 +1573,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -1127,10 +1585,10 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I18" t="s">
         <v>13</v>
@@ -1138,25 +1596,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I19" t="s">
         <v>9</v>
@@ -1164,22 +1622,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -1190,22 +1648,22 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s">
         <v>9</v>
@@ -1213,7 +1671,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -1228,7 +1686,7 @@
         <v>12</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I22" t="s">
         <v>13</v>
@@ -1236,25 +1694,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s">
         <v>9</v>
@@ -1262,22 +1720,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s">
         <v>9</v>
@@ -1285,7 +1743,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -1300,7 +1758,7 @@
         <v>12</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s">
         <v>13</v>
@@ -1308,10 +1766,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1320,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
         <v>13</v>
@@ -1331,10 +1789,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
@@ -1343,17 +1801,1125 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" t="s">
+        <v>99</v>
+      </c>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" t="s">
+        <v>106</v>
+      </c>
+      <c r="I31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>198</v>
+      </c>
+      <c r="H32" t="s">
+        <v>181</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s">
+        <v>191</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>192</v>
+      </c>
+      <c r="H34" t="s">
+        <v>182</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>200</v>
+      </c>
+      <c r="H36" t="s">
+        <v>183</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" t="s">
+        <v>194</v>
+      </c>
+      <c r="G37" t="s">
+        <v>63</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>195</v>
+      </c>
+      <c r="H38" t="s">
+        <v>184</v>
+      </c>
+      <c r="I38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>98</v>
+      </c>
+      <c r="H39" t="s">
+        <v>185</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F40" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40" t="s">
+        <v>196</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>199</v>
+      </c>
+      <c r="H42" t="s">
+        <v>186</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" t="s">
+        <v>155</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F50" t="s">
+        <v>215</v>
+      </c>
+      <c r="G50" t="s">
+        <v>221</v>
+      </c>
+      <c r="I50" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G51" t="s">
+        <v>222</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G52" t="s">
+        <v>220</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H53" t="s">
+        <v>190</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G54" t="s">
+        <v>219</v>
+      </c>
+      <c r="I54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>175</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" t="s">
+        <v>239</v>
+      </c>
+      <c r="G56" t="s">
+        <v>224</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="F58" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" t="s">
+        <v>227</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H59" t="s">
+        <v>228</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H60" t="s">
+        <v>203</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H61" t="s">
+        <v>204</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H62" t="s">
+        <v>229</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H63" t="s">
+        <v>230</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F64" t="s">
+        <v>242</v>
+      </c>
+      <c r="G64" t="s">
+        <v>238</v>
+      </c>
+      <c r="I64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B66" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>244</v>
+      </c>
+      <c r="H66" t="s">
+        <v>231</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="F67" t="s">
+        <v>245</v>
+      </c>
+      <c r="H67" t="s">
+        <v>233</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>246</v>
+      </c>
+      <c r="H68" t="s">
+        <v>232</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+      <c r="E69"/>
+      <c r="F69" t="s">
+        <v>199</v>
+      </c>
+      <c r="G69"/>
+      <c r="H69" t="s">
+        <v>234</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B71" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>170</v>
+      </c>
+      <c r="B72" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Léo\Documents\Pathfinder\Campagne des Tempêtes\Construction de royaumes\Simulations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A625B4-7149-4767-BC4B-686C8FD05A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D84373-4B69-4110-BBC2-98C493401661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CBB80B22-E302-4148-88F2-18F13870AE8F}"/>
+    <workbookView xWindow="-51720" yWindow="-2010" windowWidth="51840" windowHeight="21120" xr2:uid="{CBB80B22-E302-4148-88F2-18F13870AE8F}"/>
   </bookViews>
   <sheets>
     <sheet name="projets" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="249">
   <si>
     <t>id</t>
   </si>
@@ -575,12 +575,6 @@
     <t>Produire potions</t>
   </si>
   <si>
-    <t>FIBRE=6</t>
-  </si>
-  <si>
-    <t>PIERRE=6</t>
-  </si>
-  <si>
     <t>Améliorer</t>
   </si>
   <si>
@@ -788,7 +782,10 @@
     <t>FIBRE=2;BOIS=1;PIERRE=1</t>
   </si>
   <si>
-    <t>BOIS=6</t>
+    <t>PIERRE=4</t>
+  </si>
+  <si>
+    <t>FIBRE=4</t>
   </si>
 </sst>
 </file>
@@ -824,8 +821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1161,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B33A7991-BA04-471F-B7E5-9B4EA1B69C5B}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -1329,7 +1325,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>249</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
@@ -1372,7 +1368,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="I9" t="s">
         <v>9</v>
@@ -1415,7 +1411,7 @@
         <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>178</v>
+        <v>248</v>
       </c>
       <c r="I11" t="s">
         <v>9</v>
@@ -1565,7 +1561,7 @@
         <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I17" t="s">
         <v>9</v>
@@ -1876,7 +1872,7 @@
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H30" t="s">
         <v>104</v>
@@ -1925,12 +1921,12 @@
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H32" t="s">
-        <v>181</v>
-      </c>
-      <c r="I32" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I32" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1947,16 +1943,16 @@
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>181</v>
+      <c r="E33" t="s">
+        <v>179</v>
       </c>
       <c r="F33" t="s">
         <v>53</v>
       </c>
       <c r="G33" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I33" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1974,12 +1970,12 @@
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H34" t="s">
-        <v>182</v>
-      </c>
-      <c r="I34" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1996,16 +1992,16 @@
       <c r="D35">
         <v>2</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>182</v>
+      <c r="E35" t="s">
+        <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2016,19 +2012,19 @@
       <c r="B36" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H36" t="s">
-        <v>183</v>
-      </c>
-      <c r="I36" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I36" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2036,25 +2032,25 @@
       <c r="A37" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>148</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>16</v>
       </c>
       <c r="D37">
         <v>2</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>183</v>
+      <c r="E37" t="s">
+        <v>181</v>
       </c>
       <c r="F37" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G37" t="s">
         <v>63</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2065,17 +2061,17 @@
       <c r="B38" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I38" t="s">
         <v>13</v>
@@ -2088,7 +2084,7 @@
       <c r="B39" t="s">
         <v>150</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39">
@@ -2098,9 +2094,9 @@
         <v>98</v>
       </c>
       <c r="H39" t="s">
-        <v>185</v>
-      </c>
-      <c r="I39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I39" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2108,7 +2104,7 @@
       <c r="A40" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>150</v>
       </c>
       <c r="C40" t="s">
@@ -2117,16 +2113,16 @@
       <c r="D40">
         <v>2</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>185</v>
+      <c r="E40" t="s">
+        <v>183</v>
       </c>
       <c r="F40" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G40" t="s">
-        <v>196</v>
-      </c>
-      <c r="I40" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2134,7 +2130,7 @@
       <c r="A41" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>150</v>
       </c>
       <c r="C41" t="s">
@@ -2143,17 +2139,16 @@
       <c r="D41">
         <v>2</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1" t="s">
+      <c r="E41" t="s">
+        <v>183</v>
+      </c>
+      <c r="F41" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" t="s">
+        <v>199</v>
+      </c>
+      <c r="I41" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2161,7 +2156,7 @@
       <c r="A42" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>151</v>
       </c>
       <c r="C42" t="s">
@@ -2171,12 +2166,12 @@
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H42" t="s">
-        <v>186</v>
-      </c>
-      <c r="I42" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I42" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2187,21 +2182,19 @@
       <c r="B43" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>11</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I43" s="1" t="s">
+      <c r="F43" t="s">
+        <v>204</v>
+      </c>
+      <c r="H43" t="s">
+        <v>185</v>
+      </c>
+      <c r="I43" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2212,21 +2205,19 @@
       <c r="B44" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44">
         <v>2</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1" t="s">
+      <c r="F44" t="s">
         <v>205</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="H44" t="s">
+        <v>203</v>
+      </c>
+      <c r="I44" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2237,21 +2228,19 @@
       <c r="B45" t="s">
         <v>154</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>11</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I45" s="1" t="s">
+      <c r="F45" t="s">
+        <v>206</v>
+      </c>
+      <c r="H45" t="s">
+        <v>186</v>
+      </c>
+      <c r="I45" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2268,15 +2257,13 @@
       <c r="D46">
         <v>2</v>
       </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
+      <c r="F46" t="s">
+        <v>207</v>
+      </c>
+      <c r="H46" t="s">
         <v>209</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2293,15 +2280,13 @@
       <c r="D47">
         <v>3</v>
       </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1" t="s">
+      <c r="F47" t="s">
+        <v>208</v>
+      </c>
+      <c r="H47" t="s">
         <v>210</v>
       </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2309,7 +2294,7 @@
       <c r="A48" t="s">
         <v>126</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>147</v>
       </c>
       <c r="C48" t="s">
@@ -2318,15 +2303,13 @@
       <c r="D48">
         <v>1</v>
       </c>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
+      <c r="F48" t="s">
         <v>63</v>
       </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I48" s="1" t="s">
+      <c r="H48" t="s">
+        <v>187</v>
+      </c>
+      <c r="I48" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2334,24 +2317,22 @@
       <c r="A49" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>11</v>
       </c>
       <c r="D49">
         <v>2</v>
       </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="F49" t="s">
+        <v>197</v>
+      </c>
+      <c r="H49" t="s">
+        <v>211</v>
+      </c>
+      <c r="I49" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2359,52 +2340,52 @@
       <c r="A50" t="s">
         <v>127</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>146</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>180</v>
+      <c r="C50" t="s">
+        <v>178</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" t="s">
+        <v>211</v>
+      </c>
+      <c r="F50" t="s">
         <v>213</v>
       </c>
-      <c r="F50" t="s">
-        <v>215</v>
-      </c>
       <c r="G50" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I50" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>128</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>146</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>180</v>
+      <c r="C51" t="s">
+        <v>178</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>216</v>
+      <c r="E51" t="s">
+        <v>211</v>
+      </c>
+      <c r="F51" t="s">
+        <v>214</v>
       </c>
       <c r="G51" t="s">
-        <v>222</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
+      </c>
+      <c r="I51" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2414,23 +2395,23 @@
       <c r="B52" t="s">
         <v>146</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>180</v>
+      <c r="C52" t="s">
+        <v>178</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>217</v>
+      <c r="E52" t="s">
+        <v>211</v>
+      </c>
+      <c r="F52" t="s">
+        <v>215</v>
       </c>
       <c r="G52" t="s">
-        <v>220</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
+      </c>
+      <c r="I52" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2440,19 +2421,19 @@
       <c r="B53" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>11</v>
       </c>
       <c r="D53">
         <v>2</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>218</v>
+      <c r="F53" t="s">
+        <v>216</v>
       </c>
       <c r="H53" t="s">
-        <v>190</v>
-      </c>
-      <c r="I53" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I53" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2463,17 +2444,17 @@
       <c r="B54" t="s">
         <v>143</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>16</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>190</v>
+      <c r="E54" t="s">
+        <v>188</v>
       </c>
       <c r="G54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I54" t="s">
         <v>9</v>
@@ -2486,21 +2467,19 @@
       <c r="B55" t="s">
         <v>144</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55">
         <v>2</v>
       </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="I55" s="1" t="s">
+      <c r="F55" t="s">
+        <v>221</v>
+      </c>
+      <c r="H55" t="s">
+        <v>200</v>
+      </c>
+      <c r="I55" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2508,51 +2487,51 @@
       <c r="A56" t="s">
         <v>175</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>144</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>177</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>202</v>
+      <c r="E56" t="s">
+        <v>200</v>
       </c>
       <c r="F56" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G56" t="s">
-        <v>224</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
+      </c>
+      <c r="I56" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>174</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>144</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>176</v>
       </c>
       <c r="D57">
         <v>2</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="I57" s="1" t="s">
+      <c r="E57" t="s">
+        <v>200</v>
+      </c>
+      <c r="F57" t="s">
+        <v>223</v>
+      </c>
+      <c r="G57" t="s">
+        <v>224</v>
+      </c>
+      <c r="I57" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2563,19 +2542,19 @@
       <c r="B58" t="s">
         <v>145</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>11</v>
       </c>
       <c r="D58">
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H58" t="s">
-        <v>227</v>
-      </c>
-      <c r="I58" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I58" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2586,19 +2565,19 @@
       <c r="B59" t="s">
         <v>156</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>11</v>
       </c>
       <c r="D59">
         <v>3</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>243</v>
+      <c r="F59" t="s">
+        <v>241</v>
       </c>
       <c r="H59" t="s">
-        <v>228</v>
-      </c>
-      <c r="I59" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I59" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2609,19 +2588,19 @@
       <c r="B60" t="s">
         <v>157</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>11</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>243</v>
+      <c r="F60" t="s">
+        <v>241</v>
       </c>
       <c r="H60" t="s">
-        <v>203</v>
-      </c>
-      <c r="I60" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I60" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2632,19 +2611,19 @@
       <c r="B61" t="s">
         <v>158</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>11</v>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>243</v>
+      <c r="F61" t="s">
+        <v>241</v>
       </c>
       <c r="H61" t="s">
-        <v>204</v>
-      </c>
-      <c r="I61" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I61" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2655,19 +2634,19 @@
       <c r="B62" t="s">
         <v>159</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>11</v>
       </c>
       <c r="D62">
         <v>3</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>243</v>
+      <c r="F62" t="s">
+        <v>241</v>
       </c>
       <c r="H62" t="s">
-        <v>229</v>
-      </c>
-      <c r="I62" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I62" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2678,19 +2657,19 @@
       <c r="B63" t="s">
         <v>160</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>11</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" t="s">
         <v>98</v>
       </c>
       <c r="H63" t="s">
-        <v>230</v>
-      </c>
-      <c r="I63" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I63" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2698,194 +2677,189 @@
       <c r="A64" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
         <v>160</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>16</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>230</v>
+      <c r="E64" t="s">
+        <v>228</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G64" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I64" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>166</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>160</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>16</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65">
         <v>1</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1" t="s">
-        <v>214</v>
+      <c r="E65" t="s">
+        <v>228</v>
+      </c>
+      <c r="F65" t="s">
+        <v>246</v>
+      </c>
+      <c r="G65" t="s">
+        <v>245</v>
+      </c>
+      <c r="I65" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>161</v>
       </c>
       <c r="B66" t="s">
         <v>168</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66">
         <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H66" t="s">
-        <v>231</v>
-      </c>
-      <c r="I66" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I66" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>162</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>168</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67">
         <v>4</v>
       </c>
       <c r="F67" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H67" t="s">
-        <v>233</v>
-      </c>
-      <c r="I67" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I67" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>168</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="1">
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68">
         <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H68" t="s">
-        <v>232</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I68" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>163</v>
       </c>
       <c r="B69" t="s">
         <v>141</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>11</v>
       </c>
       <c r="D69">
         <v>2</v>
       </c>
-      <c r="E69"/>
       <c r="F69" t="s">
-        <v>199</v>
-      </c>
-      <c r="G69"/>
+        <v>197</v>
+      </c>
       <c r="H69" t="s">
-        <v>234</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I69" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>164</v>
       </c>
       <c r="B70" t="s">
         <v>142</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>11</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="I70" s="1" t="s">
+      <c r="F70" t="s">
+        <v>241</v>
+      </c>
+      <c r="H70" t="s">
+        <v>233</v>
+      </c>
+      <c r="I70" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>165</v>
       </c>
       <c r="B71" t="s">
         <v>169</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71">
         <v>4</v>
       </c>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="I71" s="1" t="s">
+      <c r="F71" t="s">
+        <v>241</v>
+      </c>
+      <c r="H71" t="s">
+        <v>235</v>
+      </c>
+      <c r="I71" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2896,30 +2870,21 @@
       <c r="B72" t="s">
         <v>171</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72">
         <v>4</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
+      <c r="F72" t="s">
+        <v>241</v>
+      </c>
+      <c r="H72" t="s">
+        <v>234</v>
+      </c>
+      <c r="I72" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
